--- a/wagon-park/Wagon-Park-Kazakhstan.xlsx
+++ b/wagon-park/Wagon-Park-Kazakhstan.xlsx
@@ -33,6 +33,7 @@
     <definedName name="g_rate_o">Вводы!$B$34</definedName>
     <definedName name="ins">Вводы!$B$7</definedName>
     <definedName name="life">Вводы!$B$5</definedName>
+    <definedName name="life_hopper">Вводы!$B$16</definedName>
     <definedName name="life_used">Вводы!$B$26</definedName>
     <definedName name="loan_share">Вводы!$B$10</definedName>
     <definedName name="loan_years">Вводы!$B$11</definedName>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="258">
   <si>
     <t>Вводы модели — жёлтые ячейки можно менять</t>
   </si>
@@ -92,7 +93,7 @@
     <t>тенге за 1 рубль</t>
   </si>
   <si>
-    <t>Официальный курс НБК на 5 октября 2026</t>
+    <t>Официальный курс НБК на 8 октября 2026: 5,24 тенге за рубль</t>
   </si>
   <si>
     <t>tax</t>
@@ -110,7 +111,7 @@
     <t>лет</t>
   </si>
   <si>
-    <t>Назначенный срок службы современного грузового вагона колеи 1520. Сверять по паспорту модели</t>
+    <t>Срок службы крытого 11-1268 по КП и платформы 13-6953 по опубликованной характеристике. Хоппер 19-3255 — отдельная ячейка life_hopper, 30 лет</t>
   </si>
   <si>
     <t>residual</t>
@@ -182,25 +183,31 @@
     <t>Допущение: постоянные расходы при парке около 500 вагонов</t>
   </si>
   <si>
+    <t>life_hopper</t>
+  </si>
+  <si>
+    <t>КП ТОО «Railway Alliance» от 08.10.2026, модель 19-3255: назначенный срок службы 30 лет</t>
+  </si>
+  <si>
     <t>Цены и содержание одного вагона</t>
   </si>
   <si>
-    <t>Зерновоз, цена нового, руб.</t>
-  </si>
-  <si>
-    <t>Обзор «Паровоз Лизинг», июль 2025: 5,08 млн руб. после снижения с 5,90</t>
-  </si>
-  <si>
-    <t>Крытый 23,5 тс, цена нового, руб.</t>
-  </si>
-  <si>
-    <t>Тот же обзор, июль 2025: 5,60 млн. Отдельной цены большекубового с люками на крыше в открытом источнике нет — используется как ориентир</t>
-  </si>
-  <si>
-    <t>Полувагон 25 тс, цена нового, руб.</t>
-  </si>
-  <si>
-    <t>Тот же обзор, июль 2025: 5,73 млн после снижения с 6,60</t>
+    <t>Хоппер 19-3255, цена нового, руб. FCA</t>
+  </si>
+  <si>
+    <t>КП ТОО «Railway Alliance» исх. № 183 от 08.10.2026 для ТОО «Integra Logistics»: 4 450 000 руб. FCA, самовывоз. НДС в письме не оговорён</t>
+  </si>
+  <si>
+    <t>Крытый 11-1268, цена нового, руб. FCA</t>
+  </si>
+  <si>
+    <t>То же КП: 4 950 000 руб. FCA. Большекубовый крытый 174 м³, 4 люка на крыше</t>
+  </si>
+  <si>
+    <t>Платформа 13-6953, цена нового, руб. FCA</t>
+  </si>
+  <si>
+    <t>То же КП: 4 300 000 руб. FCA. Фитинговая платформа под контейнеры и танк-контейнеры, рама 13,4 м</t>
   </si>
   <si>
     <t>Цена б/у к цене нового</t>
@@ -209,22 +216,22 @@
     <t>Допущение: открытого индекса вторичного рынка на октябрь 2026 нет</t>
   </si>
   <si>
-    <t>Содержание зерновоза, руб./год</t>
-  </si>
-  <si>
-    <t>Сборка: ДР 130 тыс. без запчастей (2025) + допущение по запчастям, КР 400–500 тыс. раз в 12 лет</t>
-  </si>
-  <si>
-    <t>Содержание крытого, руб./год</t>
+    <t>Содержание хоппера 19-3255, руб./год</t>
+  </si>
+  <si>
+    <t>Сборка как у крытого хоппера: ДР около 130 тыс. без запчастей (2025) + допущение по запчастям, КР 400–500 тыс. раз в 12 лет. Отдельной калькуляции ремонта 19-3255 в открытом доступе нет</t>
+  </si>
+  <si>
+    <t>Содержание крытого 11-1268, руб./год</t>
   </si>
   <si>
     <t>Та же логика, КР крытого 450–600 тыс.</t>
   </si>
   <si>
-    <t>Содержание полувагона, руб./год</t>
-  </si>
-  <si>
-    <t>879 руб./сутки × 365. АО «ОЖдПС», динамика 2024→2025: с 708 до 879 руб./сутки</t>
+    <t>Содержание платформы 13-6953, руб./год</t>
+  </si>
+  <si>
+    <t>Допущение, не суточная ставка ОЖдПС. ДР 130 тыс. без запчастей раз в 3 года, запчасти приняты равными работе, КР на уровне хоппера 400 тыс. раз в 12 лет, колёса — допущение. 879 ₽/сутки относятся к полувагону и сюда не переносятся</t>
   </si>
   <si>
     <t>Надбавка к ремонту б/у</t>
@@ -245,22 +252,22 @@
     <t>Ставка — руб./сутки. Дни — сколько суток в году вагон находится в коммерческом использовании и приносит ставку. Остальные сутки ставка равна нулю, а содержание платится за весь год.</t>
   </si>
   <si>
-    <t>Зерновоз, консервативная ставка</t>
-  </si>
-  <si>
-    <t>Зерновоз, консервативные дни</t>
-  </si>
-  <si>
-    <t>Зерновоз, базовая ставка</t>
-  </si>
-  <si>
-    <t>Зерновоз, базовые дни</t>
-  </si>
-  <si>
-    <t>Зерновоз, оптимистичная ставка</t>
-  </si>
-  <si>
-    <t>Зерновоз, оптимистичные дни</t>
+    <t>Хоппер 19-3255, консервативная ставка</t>
+  </si>
+  <si>
+    <t>Хоппер 19-3255, консервативные дни</t>
+  </si>
+  <si>
+    <t>Хоппер 19-3255, базовая ставка — ЕСЛИ ЭТО ЗЕРНО</t>
+  </si>
+  <si>
+    <t>Хоппер 19-3255, базовые дни</t>
+  </si>
+  <si>
+    <t>Хоппер 19-3255, оптимистичная ставка</t>
+  </si>
+  <si>
+    <t>Хоппер 19-3255, оптимистичные дни</t>
   </si>
   <si>
     <t>Крытый, консервативная ставка</t>
@@ -281,55 +288,55 @@
     <t>Крытый, оптимистичные дни</t>
   </si>
   <si>
-    <t>Полувагон, консервативная ставка</t>
-  </si>
-  <si>
-    <t>Полувагон, консервативные дни</t>
-  </si>
-  <si>
-    <t>Полувагон, базовая ставка</t>
-  </si>
-  <si>
-    <t>Полувагон, базовые дни</t>
-  </si>
-  <si>
-    <t>Полувагон, оптимистичная ставка</t>
-  </si>
-  <si>
-    <t>Полувагон, оптимистичные дни</t>
-  </si>
-  <si>
-    <t>База зерновоза 1 700 — ниже июльской аренды 1 910 («Паровоз Лизинг») и ниже августовского спота 2 300–3 500 (ИЦО), потому что долгосрочные контракты на межсезонье не заключаются. Консерватив и оптимум — границы модели, не котировка.</t>
-  </si>
-  <si>
-    <t>Абсолютная ставка крытого вагона в открытых обзорах ИЦО и РЖД-Партнер не раскрыта, опубликовано только направление (снижение на фоне профицита и конкуренции с автотранспортом). 1 500 руб./сутки — модельное допущение между полувагоном и зерновозом. Меняйте ячейку под коммерческое предложение.</t>
-  </si>
-  <si>
-    <t>База 900 руб./сутки — долгосрочная аренда полувагона 23,5 тс в августе 2025, ИЦО (Vgudok). Консерватив 650 — нижняя граница ставки предоставления 650–1 000. Оптимум 1 260 — аренда в июле 2025 до августовского провала.</t>
+    <t>Платформа 13-6953, консервативная ставка</t>
+  </si>
+  <si>
+    <t>Платформа 13-6953, консервативные дни</t>
+  </si>
+  <si>
+    <t>Платформа 13-6953, базовая ставка</t>
+  </si>
+  <si>
+    <t>Платформа 13-6953, базовые дни</t>
+  </si>
+  <si>
+    <t>Платформа 13-6953, оптимистичная ставка</t>
+  </si>
+  <si>
+    <t>Платформа 13-6953, оптимистичные дни</t>
+  </si>
+  <si>
+    <t>КП не называет груз модели 19-3255, и модели нет в открытом реестре vagon.by. Зерновые хопперы в том же письме — другие модели. Ставка 1 700 применяется только как проверка «если паспорт разрешает зерно»: она ниже июльской аренды зерновоза 1 910 и ниже августовского спота 2 300–3 500, потому что с февраля длинные контракты не заключаются.</t>
+  </si>
+  <si>
+    <t>Последняя открытая абсолютная ставка крытого — Argus, октябрь 2024: 138 м³ 2 620–2 710 ₽, 158 м³ 2 750–2 890 ₽. ИЦО в 2025–2026 публикует только направление: ставка снижается. 1 500 ₽ для большекубового 11-1268 (174 м³) — допущение ниже печати 2024 года, не котировка.</t>
+  </si>
+  <si>
+    <t>13-6953 — фитинговая платформа с рамой 13,4 м, класс 40 футов. База 1 100 ₽ — индикатив ЦЦИ на 40-футовую платформу в июле 2026, без НДС. Консерватив 700 ₽ — верх спота августа 2025 (ИЦО: 500–700). Оптимум 1 500 ₽ — верх длинного контракта лета 2026, не дальневосточный спот 2 000–2 500.</t>
   </si>
   <si>
     <t>Размер парка для расчёта портфеля</t>
   </si>
   <si>
-    <t>Портфель 1: зерновозы</t>
-  </si>
-  <si>
-    <t>Портфель 1: крытые</t>
-  </si>
-  <si>
-    <t>Портфель 1: полувагоны</t>
-  </si>
-  <si>
-    <t>Портфель 2: зерновозы</t>
-  </si>
-  <si>
-    <t>Портфель 2: крытые</t>
-  </si>
-  <si>
-    <t>Портфель 2: полувагоны</t>
-  </si>
-  <si>
-    <t>Портфель 1 — нижняя граница запроса: 10 крытых, 10 зерновозов, 10 полувагонов. Портфель 2 — верхняя: 20 / 20 / 10.</t>
+    <t>Заказ из КП: хопперы 19-3255</t>
+  </si>
+  <si>
+    <t>Заказ из КП: крытые 11-1268</t>
+  </si>
+  <si>
+    <t>Заказ из КП: платформы 13-6953</t>
+  </si>
+  <si>
+    <t>Удвоенный заказ: хопперы</t>
+  </si>
+  <si>
+    <t>Удвоенный заказ: крытые</t>
+  </si>
+  <si>
+    <t>Удвоенный заказ: платформы</t>
+  </si>
+  <si>
+    <t>Портфель 1 — ровно заказ: 10 хопперов 19-3255, 10 крытых 11-1268, 10 платформ 13-6953. Портфель 2 — тот же набор, удвоенный. Полувагонов в заказе нет.</t>
   </si>
   <si>
     <t>Как считается один вагон</t>
@@ -344,22 +351,22 @@
     <t>Показатель</t>
   </si>
   <si>
-    <t>Зерновоз конс.</t>
-  </si>
-  <si>
-    <t>Зерновоз база</t>
-  </si>
-  <si>
-    <t>Зерновоз опт.</t>
-  </si>
-  <si>
-    <t>Крытый конс.</t>
-  </si>
-  <si>
-    <t>Крытый база</t>
-  </si>
-  <si>
-    <t>Крытый опт.</t>
+    <t>19-3255 конс.</t>
+  </si>
+  <si>
+    <t>19-3255 база</t>
+  </si>
+  <si>
+    <t>19-3255 опт.</t>
+  </si>
+  <si>
+    <t>11-1268 конс.</t>
+  </si>
+  <si>
+    <t>11-1268 база</t>
+  </si>
+  <si>
+    <t>11-1268 опт.</t>
   </si>
   <si>
     <t>Цена, руб.</t>
@@ -422,7 +429,7 @@
     <t>Денежные потоки для IRR (год 0 — покупка, последний год + остаток)</t>
   </si>
   <si>
-    <t>Полувагон</t>
+    <t>Платформа 13-6953</t>
   </si>
   <si>
     <t>Консервативный</t>
@@ -455,16 +462,16 @@
     <t>Потоки полувагона для IRR и NPV начинаются в столбцах I–K, строки 41–73. Годы после остаточного срока б/у на листе «Барьер» остаются пустыми: Excel их в IRR не включает.</t>
   </si>
   <si>
-    <t>Два парка из запроса, базовый сценарий</t>
-  </si>
-  <si>
-    <t>EBITDA одного вагона берётся из листа «Юнит»: зерновоз C11, крытый F11, полувагон C31.</t>
+    <t>Заказ из КП и тот же заказ, удвоенный. Базовый сценарий</t>
+  </si>
+  <si>
+    <t>EBITDA одного вагона берётся из листа «Юнит»: хоппер 19-3255 — C11, крытый 11-1268 — F11, платформа 13-6953 — C31. Ставка хоппера имеет смысл, только если паспорт разрешает зерно.</t>
   </si>
   <si>
     <t>10 + 10 + 10</t>
   </si>
   <si>
-    <t>20 + 20 + 10</t>
+    <t>20 + 20 + 20</t>
   </si>
   <si>
     <t>Зерновозы, шт.</t>
@@ -512,10 +519,10 @@
     <t>Порог</t>
   </si>
   <si>
-    <t>Зерновоз</t>
-  </si>
-  <si>
-    <t>Крытый</t>
+    <t>Хоппер 19-3255</t>
+  </si>
+  <si>
+    <t>Крытый 11-1268</t>
   </si>
   <si>
     <t>Дни базового сценария</t>
@@ -539,16 +546,19 @@
     <t>Рыночный ориентир, руб./сутки</t>
   </si>
   <si>
-    <t>не опубликован</t>
+    <t>1 910, если зерно</t>
+  </si>
+  <si>
+    <t>печать 2024: 2 750–2 890</t>
   </si>
   <si>
     <t>Рыночный ориентир зерновоза — аренда июля 2025, 1 910 руб./сутки («Паровоз Лизинг»), не августовский спот. Полувагон — долгосрочная аренда августа 2025, 900 руб./сутки (ИЦО). Крытый ориентир в открытом источнике отсутствует.</t>
   </si>
   <si>
-    <t>Б/у зерновоз: цена = price_grain × used_coef, содержание × (1+maint_used_uplift), срок = life_used. Поменяйте коэффициент на листе «Вводы».</t>
-  </si>
-  <si>
-    <t>Б/у зерновоз</t>
+    <t>Б/у хоппер 19-3255: цена = цена нового × used_coef, содержание × (1+maint_used_uplift), срок = life_used. Это не цена из КП: КП даёт только новый вагон. Коэффициент 50% — допущение.</t>
+  </si>
+  <si>
+    <t>Б/у хоппер 19-3255</t>
   </si>
   <si>
     <t>База</t>
@@ -569,7 +579,7 @@
     <t>Парк 20 / 50 / 100 / 300 / 500 в базовом сценарии</t>
   </si>
   <si>
-    <t>Смешанный парк повторяет пропорцию 40% зерновозы / 40% крытые / 20% полувагоны. Рядом — парк только из зерновозов, это лучший из трёх типов.</t>
+    <t>Смешанный парк повторяет заказ: по трети хопперов 19-3255, крытых 11-1268 и платформ 13-6953. Рядом — парк только из хопперов, и только при зерновой ставке.</t>
   </si>
   <si>
     <t>Постоянные расходы, тенге</t>
@@ -587,19 +597,19 @@
     <t>Смешанный парк: EBITDA после офиса</t>
   </si>
   <si>
-    <t>Только зерновозы: CAPEX, руб.</t>
-  </si>
-  <si>
-    <t>Только зерновозы: EBITDA вагонов</t>
-  </si>
-  <si>
-    <t>Только зерновозы: EBITDA после офиса</t>
+    <t>Только хопперы 19-3255: CAPEX, руб.</t>
+  </si>
+  <si>
+    <t>Только хопперы: EBITDA вагонов</t>
+  </si>
+  <si>
+    <t>Только хопперы: EBITDA после офиса</t>
   </si>
   <si>
     <t>Масштаб не лечит слабую единицу. Если один вагон не покрывает стоимость денег, пятьсот вагонов увеличивают и выручку, и замороженный капитал.</t>
   </si>
   <si>
-    <t>Покупка, кредит, лизинг — на примере одного нового зерновоза, базовый сценарий</t>
+    <t>Покупка, кредит, лизинг — один новый хоппер 19-3255, базовый сценарий, если ставка зерновая</t>
   </si>
   <si>
     <t>Свои деньги</t>
@@ -671,7 +681,13 @@
     <t>Курс</t>
   </si>
   <si>
-    <t>Национальный Банк Казахстана, официальный курс на 5 октября 2026: 1 RUB = 5,35 KZT; 1 USD = 447,73 KZT.</t>
+    <t>Национальный Банк Казахстана, официальный курс на 8 октября 2026: 1 RUB = 5,24 KZT.</t>
+  </si>
+  <si>
+    <t>Коммерческое предложение</t>
+  </si>
+  <si>
+    <t>ТОО «Railway Alliance», исх. № 183 от 08.10.2026, директору ТОО «Integra Logistics». FCA, самовывоз: хоппер 19-3255 — 4 450 000 руб., крытый 11-1268 — 4 950 000 руб., платформа 13-6953 — 4 300 000 руб. Аванс 70%, остаток 30% после акта. Срок письма — 10 дней. НДС в цене не оговорён. В том же письме, но не в расчёте: зерновой хоппер 19-3058 за 4 400 000 и хоппер 19-1274-01 за 4 300 000.</t>
   </si>
   <si>
     <t>Базовая ставка</t>
@@ -779,13 +795,19 @@
     <t>Крытые и платформы</t>
   </si>
   <si>
-    <t>ИЦО: ставки крытых снижались из-за профицита и перетока на автотранспорт; абсолют в открытом доступе не опубликован. Фиттинговые 80 фут., август 2025: долгосрочные 1 400–2 200 руб./сутки, спот 960–1 300. 40 фут.: 1 100–1 430 и 500–700.</t>
-  </si>
-  <si>
-    <t>Цены новых вагонов</t>
-  </si>
-  <si>
-    <t>«Паровоз Лизинг», июль 2025: зерновоз 5,08 млн руб., крытый 5,60 млн, полувагон 25 тс 5,73 млн, платформа 80 фут. 5,15 млн. Перекрёстная проверка: средняя цена производителя грузового вагона в РФ в марте 2026 — 5,31 млн руб. (обзор ACG).</t>
+    <t>Argus, октябрь 2024: крытый 138 м³ — 2 620–2 710 руб./сутки, 158 м³ — 2 750–2 890. ИЦО после этого публикует снижение без новой абсолютной цифры. 40-футовые фитинговые, август 2025, ИЦО: долгосрочные 1 100–1 430, спот 500–700. ЦЦИ, июль 2026: индикатив 40 футов около 1 100 руб./сутки без НДС; длинные контракты, по оценке участника рынка, 1 200–1 500; локальный спот Дальнего Востока 2 000–2 500 в базу не берётся. Выпуск фитинговых платформ в I полугодии 2026 упал на 89%, до 373 штук.</t>
+  </si>
+  <si>
+    <t>Цены этого заказа</t>
+  </si>
+  <si>
+    <t>Берутся из КП Railway Alliance от 08.10.2026, условия FCA. Июльский обзор «Паровоз Лизинг» (зерновоз 5,08 млн, крытый 5,60 млн, полувагон 5,73 млн) остаётся рыночным фоном, но в модель не входит. Средняя цена производителя грузового вагона в РФ в марте 2026 — 5,31 млн руб. (обзор ACG).</t>
+  </si>
+  <si>
+    <t>Модели</t>
+  </si>
+  <si>
+    <t>11-1268 — крытый универсальный 174 м³, 4 люка на крыше, срок 32 года, АО «Рузхиммаш» (РМ Рейл, vagon.by). 13-6953 — фитинговая платформа для контейнеров и танк-контейнеров, рама 13,4 м, грузоподъёмность 72 т, срок службы 32 года по характеристике завода; производитель — Рославльский ВРЗ. 19-3255 в открытом реестре vagon.by не найдена; груз в КП не назван, срок службы в письме — 30 лет, объём 122 м³, один загрузочный и шесть разгрузочных люков.</t>
   </si>
   <si>
     <t>Ремонт</t>
@@ -1278,7 +1300,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4">
-        <v>5.35</v>
+        <v>5.24</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>6</v>
@@ -1455,134 +1477,148 @@
         <v>36</v>
       </c>
     </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="7">
+        <v>30</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B18" s="7">
-        <v>5080000</v>
+        <v>4450000</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" s="7">
-        <v>5600000</v>
+        <v>4950000</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B20" s="7">
-        <v>5730000</v>
+        <v>4300000</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B21" s="8">
         <v>0.5</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B22" s="7">
         <v>175000</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B23" s="7">
         <v>185000</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B24" s="7">
-        <v>320835</v>
+        <v>170000</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B25" s="8">
         <v>0.2</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B26" s="7">
         <v>16</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B30" s="7">
         <v>1200</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B31" s="7">
         <v>180</v>
@@ -1590,7 +1626,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B32" s="7">
         <v>1700</v>
@@ -1598,7 +1634,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B33" s="7">
         <v>230</v>
@@ -1606,7 +1642,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B34" s="7">
         <v>2500</v>
@@ -1614,7 +1650,7 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B35" s="7">
         <v>280</v>
@@ -1622,18 +1658,18 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B36" s="7">
         <v>1100</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B37" s="7">
         <v>170</v>
@@ -1641,7 +1677,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B38" s="7">
         <v>1500</v>
@@ -1649,7 +1685,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B39" s="7">
         <v>220</v>
@@ -1657,7 +1693,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B40" s="7">
         <v>2000</v>
@@ -1665,7 +1701,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B41" s="7">
         <v>270</v>
@@ -1673,18 +1709,18 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B42" s="7">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B43" s="7">
         <v>180</v>
@@ -1692,55 +1728,55 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B44" s="7">
-        <v>900</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B45" s="7">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B46" s="7">
-        <v>1260</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B47" s="7">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B50" s="7">
         <v>10</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B51" s="7">
         <v>10</v>
@@ -1748,7 +1784,7 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B52" s="7">
         <v>10</v>
@@ -1756,7 +1792,7 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B53" s="7">
         <v>20</v>
@@ -1764,7 +1800,7 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B54" s="7">
         <v>20</v>
@@ -1772,20 +1808,20 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B55" s="7">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="78" customHeight="1">
       <c r="A58" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1804,35 +1840,35 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="I2" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I3" s="2">
         <f>B3</f>
@@ -1861,7 +1897,7 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B4" s="10">
         <f>price_grain</f>
@@ -1914,7 +1950,7 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B5" s="10">
         <f>g_rate_c</f>
@@ -1967,7 +2003,7 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B6" s="10">
         <f>g_days_c</f>
@@ -2020,7 +2056,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="11">
         <f>B5*B6</f>
@@ -2073,7 +2109,7 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B8" s="10">
         <f>maint_grain</f>
@@ -2126,7 +2162,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B9" s="10">
         <f>B4*ins</f>
@@ -2179,7 +2215,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B10" s="10">
         <f>B8+B9</f>
@@ -2232,7 +2268,7 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B11" s="11">
         <f>B7-B10</f>
@@ -2285,18 +2321,18 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B12" s="10">
-        <f>B4*(1-residual)/life</f>
+        <f>B4*(1-residual)/life_hopper</f>
         <v>0</v>
       </c>
       <c r="C12" s="10">
-        <f>C4*(1-residual)/life</f>
+        <f>C4*(1-residual)/life_hopper</f>
         <v>0</v>
       </c>
       <c r="D12" s="10">
-        <f>D4*(1-residual)/life</f>
+        <f>D4*(1-residual)/life_hopper</f>
         <v>0</v>
       </c>
       <c r="E12" s="10">
@@ -2338,7 +2374,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B13" s="10">
         <f>B11-B12</f>
@@ -2391,7 +2427,7 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B14" s="10">
         <f>MAX(B13,0)*tax</f>
@@ -2444,7 +2480,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B15" s="10">
         <f>B13-B14</f>
@@ -2497,7 +2533,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B16" s="11">
         <f>B11-B14</f>
@@ -2550,7 +2586,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B17" s="12">
         <f>IF(B11&lt;=0,"не окупается",B4/B11)</f>
@@ -2603,7 +2639,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B18" s="12">
         <f>IF(B16&lt;=0,"не окупается",B4/B16)</f>
@@ -2656,7 +2692,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B19" s="13">
         <f>IF(B7=0,NA(),B11/B7)</f>
@@ -2709,7 +2745,7 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B20" s="14">
         <f>IRR(I4:I36)</f>
@@ -2762,7 +2798,7 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B21" s="14">
         <f>IF(B4=0,NA(),B16/B4)</f>
@@ -2815,7 +2851,7 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B22" s="11">
         <f>NPV(nbk,I5:I36)+I4</f>
@@ -2868,16 +2904,16 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I23" s="10">
         <f>B16</f>
@@ -2906,7 +2942,7 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B24" s="10">
         <f>price_gondola</f>
@@ -2947,7 +2983,7 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B25" s="10">
         <f>p_rate_c</f>
@@ -2988,7 +3024,7 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B26" s="10">
         <f>p_days_c</f>
@@ -3029,7 +3065,7 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B27" s="11">
         <f>B25*B26</f>
@@ -3070,7 +3106,7 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B28" s="10">
         <f>maint_gondola</f>
@@ -3111,7 +3147,7 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B29" s="10">
         <f>B24*ins</f>
@@ -3152,7 +3188,7 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B30" s="10">
         <f>B28+B29</f>
@@ -3193,7 +3229,7 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B31" s="11">
         <f>B27-B30</f>
@@ -3234,7 +3270,7 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B32" s="10">
         <f>B24*(1-residual)/life</f>
@@ -3275,7 +3311,7 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B33" s="10">
         <f>B31-B32</f>
@@ -3316,7 +3352,7 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B34" s="10">
         <f>MAX(B33,0)*tax</f>
@@ -3331,15 +3367,15 @@
         <v>0</v>
       </c>
       <c r="I34" s="10">
-        <f>B16</f>
+        <f>B16+B4*residual</f>
         <v>0</v>
       </c>
       <c r="J34" s="10">
-        <f>C16</f>
+        <f>C16+C4*residual</f>
         <v>0</v>
       </c>
       <c r="K34" s="10">
-        <f>D16</f>
+        <f>D16+D4*residual</f>
         <v>0</v>
       </c>
       <c r="L34" s="10">
@@ -3357,7 +3393,7 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B35" s="10">
         <f>B33-B34</f>
@@ -3372,15 +3408,15 @@
         <v>0</v>
       </c>
       <c r="I35" s="10">
-        <f>B16</f>
+        <f>""</f>
         <v>0</v>
       </c>
       <c r="J35" s="10">
-        <f>C16</f>
+        <f>""</f>
         <v>0</v>
       </c>
       <c r="K35" s="10">
-        <f>D16</f>
+        <f>""</f>
         <v>0</v>
       </c>
       <c r="L35" s="10">
@@ -3398,7 +3434,7 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B36" s="11">
         <f>B31-B34</f>
@@ -3413,15 +3449,15 @@
         <v>0</v>
       </c>
       <c r="I36" s="10">
-        <f>B16+B4*residual</f>
+        <f>""</f>
         <v>0</v>
       </c>
       <c r="J36" s="10">
-        <f>C16+C4*residual</f>
+        <f>""</f>
         <v>0</v>
       </c>
       <c r="K36" s="10">
-        <f>D16+D4*residual</f>
+        <f>""</f>
         <v>0</v>
       </c>
       <c r="L36" s="10">
@@ -3439,7 +3475,7 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B37" s="12">
         <f>IF(B31&lt;=0,"не окупается",B24/B31)</f>
@@ -3456,7 +3492,7 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B38" s="14">
         <f>IRR(I41:I73)</f>
@@ -3473,7 +3509,7 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B39" s="14">
         <f>IF(B24=0,NA(),B36/B24)</f>
@@ -3490,7 +3526,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B40" s="11">
         <f>NPV(nbk,I42:I73)+I41</f>
@@ -3507,7 +3543,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I41" s="10">
         <f>-B24</f>
@@ -3986,28 +4022,28 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B5" s="10">
         <f>q1_grain</f>
@@ -4020,7 +4056,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B6" s="10">
         <f>q1_covered</f>
@@ -4033,7 +4069,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B7" s="10">
         <f>q1_gondola</f>
@@ -4046,7 +4082,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B8" s="11">
         <f>B5*price_grain+B6*price_covered+B7*price_gondola</f>
@@ -4059,7 +4095,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" s="10">
         <f>B8*fx/1000000</f>
@@ -4072,7 +4108,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B10" s="10">
         <f>B5*'Юнит'!C7+B6*'Юнит'!F7+B7*'Юнит'!C27</f>
@@ -4085,7 +4121,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B11" s="11">
         <f>B5*'Юнит'!C11+B6*'Юнит'!F11+B7*'Юнит'!C31</f>
@@ -4098,7 +4134,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B12" s="10">
         <f>overhead_small/fx</f>
@@ -4111,7 +4147,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B13" s="11">
         <f>B11-B12</f>
@@ -4124,7 +4160,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B14" s="10">
         <f>IF(B11&lt;=0,"не окупается",B8/B11)</f>
@@ -4137,7 +4173,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B15" s="10">
         <f>IF(B13&lt;=0,"не окупается",B8/B13)</f>
@@ -4150,29 +4186,29 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="32" customHeight="1"/>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B21" s="11">
         <f>B5*'Юнит'!D11+B6*'Юнит'!G11+B7*'Юнит'!D31</f>
@@ -4185,7 +4221,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B22" s="11">
         <f>B21-B12</f>
@@ -4198,7 +4234,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B23" s="12">
         <f>IF(B22&lt;=0,"не окупается",B8/B22)</f>
@@ -4225,31 +4261,31 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B5" s="10">
         <f>'Юнит'!C6</f>
@@ -4266,7 +4302,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" s="10">
         <f>'Юнит'!C10</f>
@@ -4283,7 +4319,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B7" s="10">
         <f>B6/B5</f>
@@ -4300,7 +4336,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B8" s="10">
         <f>('Юнит'!C4/8+B6)/B5</f>
@@ -4317,7 +4353,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B9" s="10">
         <f>('Юнит'!C4/10+B6)/B5</f>
@@ -4334,7 +4370,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B10" s="10">
         <f>('Юнит'!C4/12+B6)/B5</f>
@@ -4351,7 +4387,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B11" s="10">
         <f>('Юнит'!C4/15+B6)/B5</f>
@@ -4368,43 +4404,43 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B12" s="10">
-        <v>1910</v>
+        <v>157</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D12" s="10">
-        <v>900</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="32" customHeight="1"/>
     <row r="15" spans="1:4">
       <c r="A15" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B18" s="10">
         <f>price_grain*used_coef</f>
@@ -4417,7 +4453,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B19" s="10">
         <f>maint_grain*(1+maint_used_uplift)</f>
@@ -4430,7 +4466,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B20" s="10">
         <f>B19+B18*ins</f>
@@ -4443,7 +4479,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B21" s="10">
         <f>g_rate_b*g_days_b</f>
@@ -4456,7 +4492,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B22" s="11">
         <f>B21-B20</f>
@@ -4469,7 +4505,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B23" s="12">
         <f>IF(B22&lt;=0,"не окупается",B18/B22)</f>
@@ -4482,7 +4518,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B24" s="10">
         <f>B18*(1-residual)/life_used</f>
@@ -4495,7 +4531,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B25" s="10">
         <f>B22-B24</f>
@@ -4508,7 +4544,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B26" s="10">
         <f>MAX(B25,0)*tax</f>
@@ -4521,7 +4557,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B27" s="11">
         <f>B22-B26</f>
@@ -4534,7 +4570,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B28" s="14">
         <f>IF(B18=0,NA(),B27/B18)</f>
@@ -4547,7 +4583,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B29" s="14">
         <f>IRR(H40:H72)</f>
@@ -4560,7 +4596,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B30" s="11">
         <f>NPV(nbk,H41:H72)+H40</f>
@@ -4573,15 +4609,15 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="8:9">
       <c r="H39" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="8:9">
@@ -4930,12 +4966,12 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4958,7 +4994,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B5" s="10">
         <f>overhead_small</f>
@@ -4983,7 +5019,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B6" s="10">
         <f>B5/fx</f>
@@ -5008,57 +5044,57 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B8" s="10">
-        <f>20*(0.4*price_grain+0.4*price_covered+0.2*price_gondola)</f>
+        <f>20*((price_grain+price_covered+price_gondola)/3)</f>
         <v>0</v>
       </c>
       <c r="C8" s="10">
-        <f>50*(0.4*price_grain+0.4*price_covered+0.2*price_gondola)</f>
+        <f>50*((price_grain+price_covered+price_gondola)/3)</f>
         <v>0</v>
       </c>
       <c r="D8" s="10">
-        <f>100*(0.4*price_grain+0.4*price_covered+0.2*price_gondola)</f>
+        <f>100*((price_grain+price_covered+price_gondola)/3)</f>
         <v>0</v>
       </c>
       <c r="E8" s="10">
-        <f>300*(0.4*price_grain+0.4*price_covered+0.2*price_gondola)</f>
+        <f>300*((price_grain+price_covered+price_gondola)/3)</f>
         <v>0</v>
       </c>
       <c r="F8" s="10">
-        <f>500*(0.4*price_grain+0.4*price_covered+0.2*price_gondola)</f>
+        <f>500*((price_grain+price_covered+price_gondola)/3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B9" s="10">
-        <f>20*(0.4*'Юнит'!C11+0.4*'Юнит'!F11+0.2*'Юнит'!C31)</f>
+        <f>20*(('Юнит'!C11+'Юнит'!F11+'Юнит'!C31)/3)</f>
         <v>0</v>
       </c>
       <c r="C9" s="10">
-        <f>50*(0.4*'Юнит'!C11+0.4*'Юнит'!F11+0.2*'Юнит'!C31)</f>
+        <f>50*(('Юнит'!C11+'Юнит'!F11+'Юнит'!C31)/3)</f>
         <v>0</v>
       </c>
       <c r="D9" s="10">
-        <f>100*(0.4*'Юнит'!C11+0.4*'Юнит'!F11+0.2*'Юнит'!C31)</f>
+        <f>100*(('Юнит'!C11+'Юнит'!F11+'Юнит'!C31)/3)</f>
         <v>0</v>
       </c>
       <c r="E9" s="10">
-        <f>300*(0.4*'Юнит'!C11+0.4*'Юнит'!F11+0.2*'Юнит'!C31)</f>
+        <f>300*(('Юнит'!C11+'Юнит'!F11+'Юнит'!C31)/3)</f>
         <v>0</v>
       </c>
       <c r="F9" s="10">
-        <f>500*(0.4*'Юнит'!C11+0.4*'Юнит'!F11+0.2*'Юнит'!C31)</f>
+        <f>500*(('Юнит'!C11+'Юнит'!F11+'Юнит'!C31)/3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B10" s="11">
         <f>B9-B6</f>
@@ -5083,7 +5119,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B11" s="12">
         <f>IF(B10&lt;=0,"не окупается",B8/B10)</f>
@@ -5108,7 +5144,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B13" s="10">
         <f>20*price_grain</f>
@@ -5133,7 +5169,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B14" s="10">
         <f>20*'Юнит'!C11</f>
@@ -5158,7 +5194,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B15" s="11">
         <f>B14-B6</f>
@@ -5183,7 +5219,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B16" s="12">
         <f>IF(B15&lt;=0,"не окупается",B13/B15)</f>
@@ -5208,7 +5244,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -5227,27 +5263,27 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B4" s="10">
         <f>price_grain</f>
@@ -5262,12 +5298,12 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B5" s="10">
         <f>price_grain</f>
@@ -5282,15 +5318,15 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C6" s="13">
         <f>nbk+bank_spread</f>
@@ -5300,12 +5336,12 @@
         <v>0.22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B7" s="10">
         <v>0</v>
@@ -5325,7 +5361,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B8" s="11">
         <f>'Юнит'!C11</f>
@@ -5340,12 +5376,12 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B9" s="11">
         <f>B8-B7</f>
@@ -5362,10 +5398,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C10" s="12">
         <f>IF(C7=0,"—",C8/C7)</f>
@@ -5378,7 +5414,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B11" s="14">
         <f>IF(B5=0,NA(),B9/B5)</f>
@@ -5395,7 +5431,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B12" s="10">
         <v>0</v>
@@ -5411,7 +5447,7 @@
     </row>
     <row r="13" spans="1:5" ht="64" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -5421,7 +5457,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -5430,191 +5466,207 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="36" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="36" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="36" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="36" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="36" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="36" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="36" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="36" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="36" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="36" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="36" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="36" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="36" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="36" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="36" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="36" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="36" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="36" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="36" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="36" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="36" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="36" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>242</v>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="36" customHeight="1">
+      <c r="A26" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="36" customHeight="1">
+      <c r="A27" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -5632,42 +5684,42 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="9" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/wagon-park/Wagon-Park-Kazakhstan.xlsx
+++ b/wagon-park/Wagon-Park-Kazakhstan.xlsx
@@ -21,25 +21,25 @@
     <definedName name="c_days_b">Вводы!$B$39</definedName>
     <definedName name="c_days_c">Вводы!$B$37</definedName>
     <definedName name="c_days_o">Вводы!$B$41</definedName>
-    <definedName name="c_rate_b">Вводы!$B$38</definedName>
-    <definedName name="c_rate_c">Вводы!$B$36</definedName>
-    <definedName name="c_rate_o">Вводы!$B$40</definedName>
+    <definedName name="c_rate_b">Вводы!$B$38*(1+vat)*fx</definedName>
+    <definedName name="c_rate_c">Вводы!$B$36*(1+vat)*fx</definedName>
+    <definedName name="c_rate_o">Вводы!$B$40*(1+vat)*fx</definedName>
     <definedName name="fx">Вводы!$B$3</definedName>
     <definedName name="g_days_b">Вводы!$B$33</definedName>
     <definedName name="g_days_c">Вводы!$B$31</definedName>
     <definedName name="g_days_o">Вводы!$B$35</definedName>
-    <definedName name="g_rate_b">Вводы!$B$32</definedName>
-    <definedName name="g_rate_c">Вводы!$B$30</definedName>
-    <definedName name="g_rate_o">Вводы!$B$34</definedName>
+    <definedName name="g_rate_b">Вводы!$B$32*(1+vat)*fx</definedName>
+    <definedName name="g_rate_c">Вводы!$B$30*(1+vat)*fx</definedName>
+    <definedName name="g_rate_o">Вводы!$B$34*(1+vat)*fx</definedName>
     <definedName name="ins">Вводы!$B$7</definedName>
     <definedName name="life">Вводы!$B$5</definedName>
     <definedName name="life_hopper">Вводы!$B$16</definedName>
     <definedName name="life_used">Вводы!$B$26</definedName>
     <definedName name="loan_share">Вводы!$B$10</definedName>
     <definedName name="loan_years">Вводы!$B$11</definedName>
-    <definedName name="maint_covered">Вводы!$B$23</definedName>
-    <definedName name="maint_gondola">Вводы!$B$24</definedName>
-    <definedName name="maint_grain">Вводы!$B$22</definedName>
+    <definedName name="maint_covered">Вводы!$B$23*(1+vat)*fx</definedName>
+    <definedName name="maint_gondola">Вводы!$B$24*(1+vat)*fx</definedName>
+    <definedName name="maint_grain">Вводы!$B$22*(1+vat)*fx</definedName>
     <definedName name="maint_used_uplift">Вводы!$B$25</definedName>
     <definedName name="nbk">Вводы!$B$8</definedName>
     <definedName name="overhead_100">Вводы!$B$13</definedName>
@@ -49,12 +49,12 @@
     <definedName name="p_days_b">Вводы!$B$45</definedName>
     <definedName name="p_days_c">Вводы!$B$43</definedName>
     <definedName name="p_days_o">Вводы!$B$47</definedName>
-    <definedName name="p_rate_b">Вводы!$B$44</definedName>
-    <definedName name="p_rate_c">Вводы!$B$42</definedName>
-    <definedName name="p_rate_o">Вводы!$B$46</definedName>
-    <definedName name="price_covered">Вводы!$B$19</definedName>
-    <definedName name="price_gondola">Вводы!$B$20</definedName>
-    <definedName name="price_grain">Вводы!$B$18</definedName>
+    <definedName name="p_rate_b">Вводы!$B$44*(1+vat)*fx</definedName>
+    <definedName name="p_rate_c">Вводы!$B$42*(1+vat)*fx</definedName>
+    <definedName name="p_rate_o">Вводы!$B$46*(1+vat)*fx</definedName>
+    <definedName name="price_covered">Вводы!$B$19*(1+vat)*fx</definedName>
+    <definedName name="price_gondola">Вводы!$B$20*(1+vat)*fx</definedName>
+    <definedName name="price_grain">Вводы!$B$18*(1+vat)*fx</definedName>
     <definedName name="q1_covered">Вводы!$B$51</definedName>
     <definedName name="q1_gondola">Вводы!$B$52</definedName>
     <definedName name="q1_grain">Вводы!$B$50</definedName>
@@ -64,13 +64,14 @@
     <definedName name="residual">Вводы!$B$6</definedName>
     <definedName name="tax">Вводы!$B$4</definedName>
     <definedName name="used_coef">Вводы!$B$21</definedName>
+    <definedName name="vat">Вводы!$B$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="258">
   <si>
     <t>Вводы модели — жёлтые ячейки можно менять</t>
   </si>
@@ -162,25 +163,25 @@
     <t>тенге в год</t>
   </si>
   <si>
-    <t>Допущение: постоянные расходы оператора при парке до 50 вагонов</t>
+    <t>В расчёте не учтены. Затраты на офис в базу не входят: ячейка равна нулю. Впишите сумму в тенге, если нужно увидеть экономику с офисом.</t>
   </si>
   <si>
     <t>overhead_100</t>
   </si>
   <si>
-    <t>Допущение: постоянные расходы при парке около 100 вагонов</t>
+    <t>В расчёте не учтены. См. overhead_small.</t>
   </si>
   <si>
     <t>overhead_300</t>
   </si>
   <si>
-    <t>Допущение: постоянные расходы при парке около 300 вагонов</t>
-  </si>
-  <si>
     <t>overhead_500</t>
   </si>
   <si>
-    <t>Допущение: постоянные расходы при парке около 500 вагонов</t>
+    <t>vat</t>
+  </si>
+  <si>
+    <t>НДС Казахстана 16% с 2026 года. Жёлтые цены КП и ставки заданы без НДС: расчётные имена умножают их на (1+vat)×курс. Если в жёлтой ячейке сумма уже с НДС, поставьте vat = 0 — останется только курс.</t>
   </si>
   <si>
     <t>life_hopper</t>
@@ -195,7 +196,7 @@
     <t>Хоппер 19-3255, цена нового, руб. FCA</t>
   </si>
   <si>
-    <t>КП ТОО «Railway Alliance» исх. № 183 от 08.10.2026 для ТОО «Integra Logistics»: 4 450 000 руб. FCA, самовывоз. НДС в письме не оговорён</t>
+    <t>КП ТОО «Railway Alliance» исх. № 183 от 08.10.2026 для ТОО «Integra Logistics»: 4 450 000 руб. FCA, самовывоз. НДС в КП не оговорён</t>
   </si>
   <si>
     <t>Крытый 11-1268, цена нового, руб. FCA</t>
@@ -249,7 +250,7 @@
     <t>Ставка и дни, когда ставка зарабатывается</t>
   </si>
   <si>
-    <t>Ставка — руб./сутки. Дни — сколько суток в году вагон находится в коммерческом использовании и приносит ставку. Остальные сутки ставка равна нулю, а содержание платится за весь год.</t>
+    <t>Жёлтая ставка — руб./сутки без НДС, как в источнике. В расчёте она становится тенге с НДС 16%. Дни — сколько суток в году вагон приносит ставку. Содержание платится за весь год. Порожний рейс платит грузоотправитель.</t>
   </si>
   <si>
     <t>Хоппер 19-3255, консервативная ставка</t>
@@ -258,7 +259,7 @@
     <t>Хоппер 19-3255, консервативные дни</t>
   </si>
   <si>
-    <t>Хоппер 19-3255, базовая ставка — ЕСЛИ ЭТО ЗЕРНО</t>
+    <t>Хоппер 19-3255, базовая ставка — зерно</t>
   </si>
   <si>
     <t>Хоппер 19-3255, базовые дни</t>
@@ -306,7 +307,7 @@
     <t>Платформа 13-6953, оптимистичные дни</t>
   </si>
   <si>
-    <t>КП не называет груз модели 19-3255, и модели нет в открытом реестре vagon.by. Зерновые хопперы в том же письме — другие модели. Ставка 1 700 применяется только как проверка «если паспорт разрешает зерно»: она ниже июльской аренды зерновоза 1 910 и ниже августовского спота 2 300–3 500, потому что с февраля длинные контракты не заключаются.</t>
+    <t>Груз хоппера 19-3255 для расчёта — зерно: так задано заказчиком. В тексте КП груз модели не напечатан. Ставка 1 700 руб./сутки без НДС — базовый ориентир зернового ряда, ниже июльской аренды 1 910 и ниже августовского спота 2 300–3 500. С февраля длинные контракты не заключаются.</t>
   </si>
   <si>
     <t>Последняя открытая абсолютная ставка крытого — Argus, октябрь 2024: 138 м³ 2 620–2 710 ₽, 158 м³ 2 750–2 890 ₽. ИЦО в 2025–2026 публикует только направление: ставка снижается. 1 500 ₽ для большекубового 11-1268 (174 м³) — допущение ниже печати 2024 года, не котировка.</t>
@@ -369,31 +370,31 @@
     <t>11-1268 опт.</t>
   </si>
   <si>
-    <t>Цена, руб.</t>
-  </si>
-  <si>
-    <t>Ставка, руб./сутки</t>
+    <t>Цена, тенге с НДС</t>
+  </si>
+  <si>
+    <t>Ставка, тенге/сутки с НДС</t>
   </si>
   <si>
     <t>Дни со ставкой</t>
   </si>
   <si>
-    <t>Выручка, руб./год</t>
-  </si>
-  <si>
-    <t>Содержание, руб./год</t>
-  </si>
-  <si>
-    <t>Страхование, руб./год</t>
-  </si>
-  <si>
-    <t>OPEX, руб./год</t>
-  </si>
-  <si>
-    <t>EBITDA, руб./год</t>
-  </si>
-  <si>
-    <t>Амортизация, руб./год</t>
+    <t>Выручка, тенге/год</t>
+  </si>
+  <si>
+    <t>Содержание, тенге/год</t>
+  </si>
+  <si>
+    <t>Страхование, тенге/год</t>
+  </si>
+  <si>
+    <t>OPEX, тенге/год</t>
+  </si>
+  <si>
+    <t>EBITDA, тенге/год</t>
+  </si>
+  <si>
+    <t>Амортизация, тенге/год</t>
   </si>
   <si>
     <t>Прибыль до налога</t>
@@ -423,7 +424,7 @@
     <t>ROI, денежный поток / цена</t>
   </si>
   <si>
-    <t>NPV при ставке НБК, руб.</t>
+    <t>NPV при ставке НБК, тенге</t>
   </si>
   <si>
     <t>Денежные потоки для IRR (год 0 — покупка, последний год + остаток)</t>
@@ -465,7 +466,7 @@
     <t>Заказ из КП и тот же заказ, удвоенный. Базовый сценарий</t>
   </si>
   <si>
-    <t>EBITDA одного вагона берётся из листа «Юнит»: хоппер 19-3255 — C11, крытый 11-1268 — F11, платформа 13-6953 — C31. Ставка хоппера имеет смысл, только если паспорт разрешает зерно.</t>
+    <t>EBITDA одного вагона берётся из листа «Юнит»: хоппер 19-3255 — C11, крытый 11-1268 — F11, платформа 13-6953 — C31. Груз хоппера — зерно. Офис в базе равен нулю.</t>
   </si>
   <si>
     <t>10 + 10 + 10</t>
@@ -483,16 +484,16 @@
     <t>Полувагоны, шт.</t>
   </si>
   <si>
-    <t>CAPEX, руб.</t>
+    <t>CAPEX, тенге с НДС</t>
   </si>
   <si>
     <t>CAPEX, млн тенге</t>
   </si>
   <si>
-    <t>EBITDA вагонов, руб./год</t>
-  </si>
-  <si>
-    <t>Постоянные расходы, руб./год</t>
+    <t>EBITDA вагонов, тенге/год</t>
+  </si>
+  <si>
+    <t>Офис, тенге/год — в базе ноль</t>
   </si>
   <si>
     <t>EBITDA после офиса</t>
@@ -504,7 +505,7 @@
     <t>Окупаемость с офисом, лет</t>
   </si>
   <si>
-    <t>Офис заложен на уровне парка до 50 вагонов (ячейка overhead_small). Если диспетчерская уже есть у экспедитора, поставьте её равной нулю и увидите экономику без содержания компании.</t>
+    <t>Затраты на офис в этих цифрах не учтены: overhead_small = 0. Любой реальный офис уменьшит EBITDA и удлинит окупаемость. Порожний рейс платит грузоотправитель. Доставка и приёмка сверх FCA в цену не входят.</t>
   </si>
   <si>
     <t>Тот же парк в оптимистичном сценарии</t>
@@ -528,7 +529,7 @@
     <t>Дни базового сценария</t>
   </si>
   <si>
-    <t>Ставка денежной безубыточности, руб./сутки</t>
+    <t>Ставка денежной безубыточности, тенге/сутки</t>
   </si>
   <si>
     <t>Ставка для окупаемости 8 лет</t>
@@ -543,13 +544,13 @@
     <t>Ставка для окупаемости 15 лет</t>
   </si>
   <si>
-    <t>Рыночный ориентир, руб./сутки</t>
-  </si>
-  <si>
-    <t>1 910, если зерно</t>
-  </si>
-  <si>
-    <t>печать 2024: 2 750–2 890</t>
+    <t>Рыночный ориентир, тенге/сутки с НДС</t>
+  </si>
+  <si>
+    <t>11 610, аренда июля 2025</t>
+  </si>
+  <si>
+    <t>печать 2024: 16,7–17,6 тыс.</t>
   </si>
   <si>
     <t>Рыночный ориентир зерновоза — аренда июля 2025, 1 910 руб./сутки («Паровоз Лизинг»), не августовский спот. Полувагон — долгосрочная аренда августа 2025, 900 руб./сутки (ИЦО). Крытый ориентир в открытом источнике отсутствует.</t>
@@ -579,16 +580,16 @@
     <t>Парк 20 / 50 / 100 / 300 / 500 в базовом сценарии</t>
   </si>
   <si>
-    <t>Смешанный парк повторяет заказ: по трети хопперов 19-3255, крытых 11-1268 и платформ 13-6953. Рядом — парк только из хопперов, и только при зерновой ставке.</t>
+    <t>Смешанный парк повторяет заказ: по трети хопперов 19-3255, крытых 11-1268 и платформ 13-6953. Рядом — парк только из зерновых хопперов. Офис в базе равен нулю.</t>
   </si>
   <si>
     <t>Постоянные расходы, тенге</t>
   </si>
   <si>
-    <t>Постоянные расходы, руб.</t>
-  </si>
-  <si>
-    <t>Смешанный парк: CAPEX, руб.</t>
+    <t>Офис в расчёте, тенге (сейчас 0)</t>
+  </si>
+  <si>
+    <t>Смешанный парк: CAPEX, тенге с НДС</t>
   </si>
   <si>
     <t>Смешанный парк: EBITDA вагонов</t>
@@ -597,7 +598,7 @@
     <t>Смешанный парк: EBITDA после офиса</t>
   </si>
   <si>
-    <t>Только хопперы 19-3255: CAPEX, руб.</t>
+    <t>Только хопперы 19-3255: CAPEX, тенге с НДС</t>
   </si>
   <si>
     <t>Только хопперы: EBITDA вагонов</t>
@@ -609,7 +610,7 @@
     <t>Масштаб не лечит слабую единицу. Если один вагон не покрывает стоимость денег, пятьсот вагонов увеличивают и выручку, и замороженный капитал.</t>
   </si>
   <si>
-    <t>Покупка, кредит, лизинг — один новый хоппер 19-3255, базовый сценарий, если ставка зерновая</t>
+    <t>Покупка, кредит, лизинг — один новый зерновой хоппер 19-3255, базовый сценарий, тенге с НДС</t>
   </si>
   <si>
     <t>Свои деньги</t>
@@ -624,13 +625,13 @@
     <t>Операционная аренда</t>
   </si>
   <si>
-    <t>Цена / объём финансирования, руб.</t>
+    <t>Цена / объём финансирования, тенге с НДС</t>
   </si>
   <si>
     <t>0, вагон не покупается</t>
   </si>
   <si>
-    <t>Собственный капитал на старте, руб.</t>
+    <t>Собственный капитал на старте, тенге</t>
   </si>
   <si>
     <t>Депозит 2 месяца ставки</t>
@@ -645,7 +646,7 @@
     <t>рыночная аренда</t>
   </si>
   <si>
-    <t>Платёж в год, руб.</t>
+    <t>Платёж в год, тенге</t>
   </si>
   <si>
     <t>EBITDA базового зерновоза</t>
@@ -663,7 +664,7 @@
     <t>Денежная доходность на собственный капитал</t>
   </si>
   <si>
-    <t>Платёж в месяц, руб.</t>
+    <t>Платёж в месяц, тенге</t>
   </si>
   <si>
     <t>Операционная аренда в столбце E — это отказ от покупки: вы платите рыночную ставку и не несёте остаточный риск. При текущем рынке спред пересдачи близок к нулю. Финансовый лизинг в модели: аванс 20%, ставка 22% годовых, срок 7 лет — допущение, не коммерческое предложение лизинговой компании. Кредит: базовый 16,25% + надбавка 5 п.п. Месячный платёж — аннуитет. Доходность на капитал здесь денежная: (EBITDA − долговой платёж) / собственные деньги на старте. Это не бухгалтерский ROE.</t>
@@ -687,7 +688,7 @@
     <t>Коммерческое предложение</t>
   </si>
   <si>
-    <t>ТОО «Railway Alliance», исх. № 183 от 08.10.2026, директору ТОО «Integra Logistics». FCA, самовывоз: хоппер 19-3255 — 4 450 000 руб., крытый 11-1268 — 4 950 000 руб., платформа 13-6953 — 4 300 000 руб. Аванс 70%, остаток 30% после акта. Срок письма — 10 дней. НДС в цене не оговорён. В том же письме, но не в расчёте: зерновой хоппер 19-3058 за 4 400 000 и хоппер 19-1274-01 за 4 300 000.</t>
+    <t>ТОО «Railway Alliance», исх. № 183 от 08.10.2026, директору ТОО «Integra Logistics». FCA, самовывоз: хоппер 19-3255 — 4 450 000 руб., крытый 11-1268 — 4 950 000 руб., платформа 13-6953 — 4 300 000 руб. Аванс 70%, остаток 30% после акта. Срок КП — 10 дней. НДС в цене не оговорён. В том же КП, но не в расчёте: зерновой хоппер 19-3058 за 4 400 000 и хоппер 19-1274-01 за 4 300 000.</t>
   </si>
   <si>
     <t>Базовая ставка</t>
@@ -1426,7 +1427,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="7">
-        <v>30000000</v>
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>29</v>
@@ -1440,7 +1441,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="7">
-        <v>45000000</v>
+        <v>0</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>29</v>
@@ -1454,27 +1455,27 @@
         <v>33</v>
       </c>
       <c r="B14" s="7">
-        <v>80000000</v>
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="7">
-        <v>120000000</v>
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1822,6 +1823,15 @@
     <row r="58" spans="1:4" ht="78" customHeight="1">
       <c r="A58" s="5" t="s">
         <v>90</v>
+      </c>
+      <c r="B58" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -4098,11 +4108,11 @@
         <v>138</v>
       </c>
       <c r="B9" s="10">
-        <f>B8*fx/1000000</f>
+        <f>B8/1000000</f>
         <v>0</v>
       </c>
       <c r="C9" s="10">
-        <f>C8*fx/1000000</f>
+        <f>C8/1000000</f>
         <v>0</v>
       </c>
     </row>
@@ -4137,11 +4147,11 @@
         <v>140</v>
       </c>
       <c r="B12" s="10">
-        <f>overhead_small/fx</f>
+        <f>overhead_small</f>
         <v>0</v>
       </c>
       <c r="C12" s="10">
-        <f>overhead_small/fx</f>
+        <f>overhead_small</f>
         <v>0</v>
       </c>
     </row>
@@ -4413,7 +4423,7 @@
         <v>159</v>
       </c>
       <c r="D12" s="10">
-        <v>1100</v>
+        <v>6686</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -5022,23 +5032,23 @@
         <v>171</v>
       </c>
       <c r="B6" s="10">
-        <f>B5/fx</f>
+        <f>B5</f>
         <v>0</v>
       </c>
       <c r="C6" s="10">
-        <f>C5/fx</f>
+        <f>C5</f>
         <v>0</v>
       </c>
       <c r="D6" s="10">
-        <f>D5/fx</f>
+        <f>D5</f>
         <v>0</v>
       </c>
       <c r="E6" s="10">
-        <f>E5/fx</f>
+        <f>E5</f>
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <f>F5/fx</f>
+        <f>F5</f>
         <v>0</v>
       </c>
     </row>
